--- a/affiliate_products.xlsx
+++ b/affiliate_products.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="390" yWindow="615" windowWidth="13095" windowHeight="7620" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Affiliate Products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Affiliate Products" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1713,6 +1713,146 @@
       <c r="F33" t="inlineStr">
         <is>
           <t>กระดาษทิชชู่ PASEO เบบี้เพียว หนา 3 ชั้น สัมผัสนุ่มละมุน อ่อนโยนต่อผิว ยกลังสุดคุ้ม</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Apple iPhone 18 Pro Max (เครื่องศูนย์ไทย ประกันศูนย์ 1 ปี) Shopee Mall</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8AWCoHKL6C</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>xxx</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Apple iPhone 18 Pro Max ชิป A20 Pro กล้องซูมคมชัด ดีไซน์พรีเมียม สั่งซื้อผ่าน Apple Flagship Store ของแท้ 100% พร้อมรับสิทธิ์ผ่อน 0% SpayLater</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>https://down-th.img.susercontent.com/file/th-11134207-81ztn-msxxsasoiscl48</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Apple iPhone 17 Pro (เครื่องศูนย์ไทย ประกันศูนย์ 1 ปี) Shopee Mall</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5AsbEphgh5</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>xxx</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Apple iPhone 17 Pro ชิป A19 Pro หน้าจอ ProMotion 120Hz แบตเตอรี่อึดยิ่งขึ้น ระบบกล้องโปร เครื่องศูนย์แท้พร้อมประกันศูนย์ไทย 1 ปีเต็ม</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://down-th.img.susercontent.com/file/th-11134207-81ztf-msuyb0tv79qff4</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>19</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Apple iPhone 16 Plus (เครื่องศูนย์ไทย ประกันศูนย์ 1 ปี) Shopee Mall</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/LnLTzHQeV</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>xxx</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Apple iPhone 16 Plus จอใหญ่เต็มตา แบตเตอรี่อึดทนทาน รองรับ Apple Intelligence เต็มรูปแบบ ชิป A18 เครื่องศูนย์ไทยแท้ ผ่อน 0% ได้</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://down-th.img.susercontent.com/file/th-11134207-81ztg-msuy0uk4gkjo7b</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>20</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Apple iPhone 15 (เครื่องศูนย์ไทย ประกันศูนย์ 1 ปี) Shopee Mall</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8fSTPKxXrZ</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>xxx</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Apple iPhone 15 พอร์ต USB-C กล้องหลัก 48MP หน้าจอ Dynamic Island สุดคุ้มค่า ใช้งานลื่นไหลยาวนาน เครื่องศูนย์ไทยแท้</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://store.storeimages.cdn-apple.com/8756/as-images.apple.com/is/iphone-15-finish-select-202309-6-1inch-black?wid=5120&amp;hei=2880&amp;fmt=p-jpg&amp;qlt=80&amp;.v=1692923777972</t>
         </is>
       </c>
     </row>

--- a/affiliate_products.xlsx
+++ b/affiliate_products.xlsx
@@ -1722,7 +1722,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Apple iPhone 18 Pro Max (เครื่องศูนย์ไทย ประกันศูนย์ 1 ปี) Shopee Mall</t>
+          <t>Apple iPhone 18 Pro Max (เครื่องศูนย์ไทย ประกันศูนย์ 1 ปี) ชิป A20 Pro ร้านค้าทางการ Shopee Mall มั่นใจได้ของแท้ 100% ประกันศูนย์ไทยเต็มปี ไม่เสี่ยงเครื่องย้อมแมว ซื้อของราคาสูงเลือกร้าน Mall อุ่นใจ ปลอดภัยที่สุด</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">

--- a/affiliate_products.xlsx
+++ b/affiliate_products.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:L55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1853,6 +1853,726 @@
       <c r="L37" t="inlineStr">
         <is>
           <t>https://store.storeimages.cdn-apple.com/8756/as-images.apple.com/is/iphone-15-finish-select-202309-6-1inch-black?wid=5120&amp;hei=2880&amp;fmt=p-jpg&amp;qlt=80&amp;.v=1692923777972</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>21</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ทีวี 32 นิ้ว ทีวี 43 นิ้ว Smart TV 4K LED โทรทัศน์ ทีวีจอแบน สมาร์ททีวี ระบบ Android ทีวีดิจิตอล รับประกัน 1ปี</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2VrqMwDZNm</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>ทีวี 32 นิ้ว ทีวี 43 นิ้ว Smart TV 4K LED โทรทัศน์ ทีวีจอแบน สมาร์ททีวี ระบบ Android ทีวีดิจิตอล รับประกัน 1ปี ราคา 3689.00 บาท</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztk-mp3uikhs59n0d1.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>22</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>New เสื้อฮู้ด Stussy Hoodie แท้100% สําหรับผู้ชาย และผู้หญิง หลวมเสื้อฮู้ด</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3B7XABAYi0</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>New เสื้อฮู้ด Stussy Hoodie แท้100% สําหรับผู้ชาย และผู้หญิง หลวมเสื้อฮู้ด ราคา 1680.00 บาท</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztk-mln7lyct3shvb7.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>23</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Lifinity ชั้นวางจาน ที่คว่ำจาน 120/105ซม ชั้นวางของในครัว</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1qc9ZkOEib</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Lifinity ชั้นวางจาน ที่คว่ำจาน 120/105ซม ชั้นวางของในครัว ราคา 678.00 บาท</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasj-m6m8v000vb5b5e.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>24</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>XTREM เคส iPhone 18/17/16/15/14 เปลี่ยนรูปได้ เคสเปลี่ยนรูป เคสไอโฟน เคสมือถือ Magnetic Screen Case NFC จอ E-Ink</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6q0pWwhhQ9</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>XTREM เคส iPhone 18/17/16/15/14 เปลี่ยนรูปได้ เคสเปลี่ยนรูป เคสไอโฟน เคสมือถือ Magnetic Screen Case NFC จอ E-Ink ราคา 2250.00 บาท</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-8259f-mt18gjog1xj6a4.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>25</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Pacsafe CX Anti-Theft Square Crossbody กระเป๋ากันขโมย กระเป๋าสะพายข้าง สำหรับเดินทางและใช้งานทุกวัน | Fits 8" Tablet</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1VzJBAKIWf</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Pacsafe CX Anti-Theft Square Crossbody กระเป๋ากันขโมย กระเป๋าสะพายข้าง สำหรับเดินทางและใช้งานทุกวัน | Fits 8" Tablet ราคา 4100.00 บาท</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zte-msmmfx079j4163.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>26</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BOYA mini 2 ไมค์ไร้สาย ตัดเสียงรบกวน AI ไมค์อัดเสียง สําหรับ Type-C iPhone/Android ไมค์ไลฟ์สด</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9AOkJG7XeU</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>BOYA mini 2 ไมค์ไร้สาย ตัดเสียงรบกวน AI ไมค์อัดเสียง สําหรับ Type-C iPhone/Android ไมค์ไลฟ์สด ราคา 1319.00 บาท</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/cn-11134207-820l4-miwe8y7c5edg26.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>27</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>[HOT]AXON Mega Smart Watch จอใหญ่AMOLED 1.85",แบตอึด,โทรได้,วัดชีพจร SpO2 ,วัดการนอน,โหมดออกกำลังกาย100+, IP68 ประกัน2ปี</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1AVOUsEit</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>[HOT]AXON Mega Smart Watch จอใหญ่AMOLED 1.85",แบตอึด,โทรได้,วัดชีพจร SpO2 ,วัดการนอน,โหมดออกกำลังกาย100+, IP68 ประกัน2ปี ราคา 1798.00 บาท</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mpj9ta3nkqvj7a.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>28</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Pacsafe GO Anti-Theft Saddle Crossbody กระเป๋ากันขโมย กระเป๋าสะพายข้าง สำหรับเดินทางและใช้งานทุกวัน</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4Vcukm6B7Q</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Pacsafe GO Anti-Theft Saddle Crossbody กระเป๋ากันขโมย กระเป๋าสะพายข้าง สำหรับเดินทางและใช้งานทุกวัน ราคา 4730.00 บาท</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-msmlbhosfs3o57.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>29</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>[ซื้อ 1 แถม 6] 2026 แท็บเล็ตพีซี 12.0 นิ้ว 12000mAh แบตเตอรี่ 4G / 5G แท็บเล็ต Dual SIM Android 12.0 แท็บเล็ต COD</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/60RiXXMOj0</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>[ซื้อ 1 แถม 6] 2026 แท็บเล็ตพีซี 12.0 นิ้ว 12000mAh แบตเตอรี่ 4G / 5G แท็บเล็ต Dual SIM Android 12.0 แท็บเล็ต COD ราคา 1799.00 บาท</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mhlffavqeo7c65.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>30</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ANCHI จักรยานพับได้ จักรยานแม่บ้าน จักรยาน แม่บ้าน ญี่ปุ่น เกียร์ 7 ระดับ ตะกร้าเหล็ก จักรยานผู้ใหญ</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4B04MAcB1P</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>ANCHI จักรยานพับได้ จักรยานแม่บ้าน จักรยาน แม่บ้าน ญี่ปุ่น เกียร์ 7 ระดับ ตะกร้าเหล็ก จักรยานผู้ใหญ ราคา 1955.00 บาท</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mlw25x1168zm9d.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>31</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Hisense TV 55 นิ้ว รุ่น 55E6Q 4K Ultra HD Smart TV Voice Control WIFI Build in Netflix</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/50ZBLhh7GG</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Hisense TV 55 นิ้ว รุ่น 55E6Q 4K Ultra HD Smart TV Voice Control WIFI Build in Netflix ราคา 9490.00 บาท</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-mt5hov1ntfr612.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>32</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>เครื่องตัดกิ่งไม้ไร้สาย ตัดแต่งพุ่มไม้ แต่งกิ่งไม้ เครื่องตัดหญ้าไฟฟ้า เลื่อยตัดแต่งสวน ตัดแต่งพุ่มหญ้า</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9KiAVfeVSA</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>เครื่องตัดกิ่งไม้ไร้สาย ตัดแต่งพุ่มไม้ แต่งกิ่งไม้ เครื่องตัดหญ้าไฟฟ้า เลื่อยตัดแต่งสวน ตัดแต่งพุ่มหญ้า ราคา 875.00 บาท</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7qul9-ljuyqy4onhnq0b.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>33</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>【รับประกัน 5ปี】elago เครื่องตัดหญ้าไฟฟ้าไร้สาย แบบพกพา ปรับได้ ยืดหด 5000mAh*2 อุปกรณ์ครบชุด พร้อมแบตเตอรีลิเธียมแท้</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5VVRwdnTF3</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>【รับประกัน 5ปี】elago เครื่องตัดหญ้าไฟฟ้าไร้สาย แบบพกพา ปรับได้ ยืดหด 5000mAh*2 อุปกรณ์ครบชุด พร้อมแบตเตอรีลิเธียมแท้ ราคา 634.00 บาท</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mq1py5gj48ox05.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>34</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>XTREM เคส iPhone 17 เปลี่ยนรูปได้ เคสเปลี่ยนรูป เคสมือถือ เคสไอโฟน Magnetic Screen Case NFC หน้าจอ E-Ink</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7fZwWdSAZ8</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>XTREM เคส iPhone 17 เปลี่ยนรูปได้ เคสเปลี่ยนรูป เคสมือถือ เคสไอโฟน Magnetic Screen Case NFC หน้าจอ E-Ink ราคา 2750.00 บาท</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztn-msy2myjf83rbdd.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>35</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>[Best Seller] TCL แอร์ Full DC SaveIn AI Inverter ประหยัดไฟ ขนาด 9,200- 24,200 BTU รุ่น TAC-XALCH2</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9zxrIvShk4</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>[Best Seller] TCL แอร์ Full DC SaveIn AI Inverter ประหยัดไฟ ขนาด 9,200- 24,200 BTU รุ่น TAC-XALCH2 ราคา 14290.00 บาท</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-msjawf9q8e808c.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>36</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>เคส iPhone 18 Pro Max 18 Pro 17 Air 16 Series Ultra Hybrid T MagFit Spigen - รองรับ Camera Control</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4VcukpE2bD</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>เคส iPhone 18 Pro Max 18 Pro 17 Air 16 Series Ultra Hybrid T MagFit Spigen - รองรับ Camera Control ราคา 1287.00 บาท</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134207-825am-msxh4293k0sp86.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>37</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>KEEN รองเท้าแตะรัดส้น ชายหญิง กันกระแทกส้นและนิ้วเท้า กันลื่นยางแท้ทุกพื้น เป่าไว ซับนิ่ม เดินป่าทางชัน</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2LYQAr4Hov</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>KEEN รองเท้าแตะรัดส้น ชายหญิง กันกระแทกส้นและนิ้วเท้า กันลื่นยางแท้ทุกพื้น เป่าไว ซับนิ่ม เดินป่าทางชัน ราคา 2429.00 บาท</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztk-moggu9b4ekn405.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>38</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2024 สไตล ์ ใหม ่ Star alpinestars a รถจักรยานยนต ์ Warm Shock-resistant Cycling Jersey Casual แจ ็ คเก ็ ตผู ้ ชายผู ้ หญิงฤดูใบไม ้ ผลิฤดูใบไม ้ ร ่ วงฤดูหนาว Soft Shell แจ ็ คเก ็ ตกันน ้ ํา Star แจ ็ คเก ็ ตสองสี</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3VkNZ0QFA2</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2024 สไตล ์ ใหม ่ Star alpinestars a รถจักรยานยนต ์ Warm Shock-resistant Cycling Jersey Casual แจ ็ คเก ็ ตผู ้ ชายผู ้ หญิงฤดูใบไม ้ ผลิฤดูใบไม ้ ร ่ วงฤดูหนาว Soft Shell แจ ็ คเก ็ ตกันน ้ ํา Star แจ ็ คเก ็ ตสองสี ราคา 2107.00 บาท</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/cn-11134207-7r98o-luf6vg0dv0xw51.webp</t>
         </is>
       </c>
     </row>
